--- a/template/GeoDataTemplate.xlsx
+++ b/template/GeoDataTemplate.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24685" windowHeight="11520"/>
+    <workbookView windowWidth="24685" windowHeight="11520" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="点" sheetId="1" r:id="rId1"/>
+    <sheet name="扇区" sheetId="2" r:id="rId2"/>
+    <sheet name="多边形" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,9 +29,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
-  <si>
-    <t>基站名称</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
+  <si>
+    <t>名称</t>
   </si>
   <si>
     <t>经度</t>
@@ -68,6 +68,18 @@
   </si>
   <si>
     <t>F河源东源森源实业</t>
+  </si>
+  <si>
+    <t>方位角</t>
+  </si>
+  <si>
+    <t>WKT</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>POLYGON ((114.655926 23.606362, 114.655537 23.606362))</t>
   </si>
 </sst>
 </file>
@@ -80,13 +92,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8.75"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Courier New"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -553,138 +571,141 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
@@ -998,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="2"/>
   <cols>
@@ -1017,145 +1038,145 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>115.164639</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="2">
         <v>23.740832</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="2">
         <v>114.962777</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="2">
         <v>24.196389</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="2">
         <v>114.79099</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="2">
         <v>24.01804</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="2">
         <v>114.79099</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="2">
         <v>24.01804</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="2">
         <v>114.73048</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="2">
         <v>23.78542</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="2">
         <v>114.784034</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="2">
         <v>23.820407</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="2">
         <v>114.76702</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="2">
         <v>23.83626</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="2">
         <v>114.84342</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="2">
         <v>24.17218</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="2">
         <v>115.11777</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="2">
         <v>24.03344</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="2">
         <v>114.7434</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="2">
         <v>23.77485</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="2">
         <v>114.7434</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="2">
         <v>23.77485</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="2">
         <v>114.7434</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="2">
         <v>23.77485</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="2">
         <v>114.778331</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="2">
         <v>23.823612</v>
       </c>
     </row>
@@ -1168,10 +1189,53 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
-  <sheetData/>
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelRow="2" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2">
+        <v>115.164639</v>
+      </c>
+      <c r="C2" s="2">
+        <v>23.740832</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2">
+        <v>114.962777</v>
+      </c>
+      <c r="C3" s="2">
+        <v>24.196389</v>
+      </c>
+      <c r="D3">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1180,10 +1244,33 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
-  <sheetData/>
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelRow="1" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
